--- a/expense-tracker-mobile/src/infrastructure/demo/fixtures/Demo_Data.xlsx
+++ b/expense-tracker-mobile/src/infrastructure/demo/fixtures/Demo_Data.xlsx
@@ -853,7 +853,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -878,6 +878,9 @@
         <v>notes</v>
       </c>
       <c r="H1" t="str">
+        <v>comments</v>
+      </c>
+      <c r="I1" t="str">
         <v>budgetId</v>
       </c>
     </row>
@@ -904,6 +907,9 @@
         <v>Budget: demo-bud-5 (Utilities pool)</v>
       </c>
       <c r="H2" t="str">
+        <v>Budget: demo-bud-5 (Utilities pool)</v>
+      </c>
+      <c r="I2" t="str">
         <v>demo-bud-5</v>
       </c>
     </row>
@@ -930,6 +936,9 @@
         <v>Budget: demo-bud-5</v>
       </c>
       <c r="H3" t="str">
+        <v>Budget: demo-bud-5</v>
+      </c>
+      <c r="I3" t="str">
         <v>demo-bud-5</v>
       </c>
     </row>
@@ -956,6 +965,9 @@
         <v>Budget: demo-bud-6 partial overlap</v>
       </c>
       <c r="H4" t="str">
+        <v>Budget: demo-bud-6 partial overlap</v>
+      </c>
+      <c r="I4" t="str">
         <v>demo-bud-6</v>
       </c>
     </row>
@@ -982,6 +994,9 @@
         <v>Budget: demo-bud-5</v>
       </c>
       <c r="H5" t="str">
+        <v>Budget: demo-bud-5</v>
+      </c>
+      <c r="I5" t="str">
         <v>demo-bud-5</v>
       </c>
     </row>
@@ -1008,6 +1023,9 @@
         <v>Budget: demo-bud-6</v>
       </c>
       <c r="H6" t="str">
+        <v>Budget: demo-bud-6</v>
+      </c>
+      <c r="I6" t="str">
         <v>demo-bud-6</v>
       </c>
     </row>
@@ -1034,6 +1052,9 @@
         <v>Budget: demo-bud-4</v>
       </c>
       <c r="H7" t="str">
+        <v>Budget: demo-bud-4</v>
+      </c>
+      <c r="I7" t="str">
         <v>demo-bud-4</v>
       </c>
     </row>
@@ -1060,6 +1081,9 @@
         <v>Budget: demo-bud-3</v>
       </c>
       <c r="H8" t="str">
+        <v>Budget: demo-bud-3</v>
+      </c>
+      <c r="I8" t="str">
         <v>demo-bud-3</v>
       </c>
     </row>
@@ -1086,19 +1110,22 @@
         <v>Budget: demo-bud-2</v>
       </c>
       <c r="H9" t="str">
+        <v>Budget: demo-bud-2</v>
+      </c>
+      <c r="I9" t="str">
         <v>demo-bud-2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:M201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1126,15 +1153,18 @@
         <v>budgetIds</v>
       </c>
       <c r="I1" t="str">
+        <v>notes</v>
+      </c>
+      <c r="J1" t="str">
         <v>comments</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>isRecurring</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>createdAtOffsetDays</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>updatedAtOffsetDays</v>
       </c>
     </row>
@@ -1164,15 +1194,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I2" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J2" t="b">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K2" t="b">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>-800</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>-800</v>
       </c>
     </row>
@@ -1202,15 +1235,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I3" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3">
+        <v>Spend note · Transit pass</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Spend note · Transit pass | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>-795</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>-795</v>
       </c>
     </row>
@@ -1240,15 +1276,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I4" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4">
+        <v>Spend note · Coffee</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Spend note · Coffee | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>-791</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>-791</v>
       </c>
     </row>
@@ -1278,15 +1317,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I5" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5">
+        <v>Spend note · Lunch</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Spend note · Lunch | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>-786</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>-786</v>
       </c>
     </row>
@@ -1316,15 +1358,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I6" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6">
+        <v>Spend note · Pharmacy</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Spend note · Pharmacy | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>-782</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>-782</v>
       </c>
     </row>
@@ -1354,15 +1399,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I7" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7">
+        <v>Spend note · Fuel</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Spend note · Fuel | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>-777</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>-777</v>
       </c>
     </row>
@@ -1392,15 +1440,18 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8">
+        <v>Spend note · Parking</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Spend note · Parking</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>-772</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>-772</v>
       </c>
     </row>
@@ -1430,15 +1481,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I9" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9">
+        <v>Spend note · Dinner · reviewed</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Spend note · Dinner · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>-768</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>-768</v>
       </c>
     </row>
@@ -1468,15 +1522,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I10" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10">
+        <v>Spend note · Books</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Spend note · Books | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>-763</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>-763</v>
       </c>
     </row>
@@ -1506,15 +1563,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I11" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11">
+        <v>Spend note · Gym</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Spend note · Gym | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>-758</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>-758</v>
       </c>
     </row>
@@ -1544,15 +1604,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I12" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12">
+        <v>Spend note · Haircut</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Spend note · Haircut | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12">
         <v>-754</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-754</v>
       </c>
     </row>
@@ -1582,15 +1645,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I13" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13">
+        <v>Spend note · Pet supplies</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Spend note · Pet supplies | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>-749</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>-749</v>
       </c>
     </row>
@@ -1620,15 +1686,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I14" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14">
+        <v>Spend note · Gift</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Spend note · Gift | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>-745</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>-745</v>
       </c>
     </row>
@@ -1658,15 +1727,18 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15">
+        <v>Spend note · Train</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Spend note · Train</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>-740</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>-740</v>
       </c>
     </row>
@@ -1696,15 +1768,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I16" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16">
+        <v>Spend note · Snacks · reviewed</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Spend note · Snacks · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16">
         <v>-735</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>-735</v>
       </c>
     </row>
@@ -1734,15 +1809,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I17" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17">
+        <v>Spend note · Clothing</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Spend note · Clothing | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>-731</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>-731</v>
       </c>
     </row>
@@ -1772,15 +1850,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I18" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18">
+        <v>Spend note · Electronics</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Spend note · Electronics | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18">
         <v>-726</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>-726</v>
       </c>
     </row>
@@ -1810,15 +1891,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I19" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19">
         <v>-721</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>-721</v>
       </c>
     </row>
@@ -1848,15 +1932,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I20" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20">
+        <v>Spend note · Taxi</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Spend note · Taxi | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20">
         <v>-717</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>-717</v>
       </c>
     </row>
@@ -1886,15 +1973,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I21" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21">
+        <v>Spend note · Water bill share</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Spend note · Water bill share | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21">
         <v>-712</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>-712</v>
       </c>
     </row>
@@ -1924,15 +2014,18 @@
         <v/>
       </c>
       <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22">
+        <v>Spend note · Office supplies</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Spend note · Office supplies</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22">
         <v>-708</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>-708</v>
       </c>
     </row>
@@ -1962,15 +2055,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I23" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23">
+        <v>Spend note · Yoga · reviewed</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Spend note · Yoga · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23">
         <v>-703</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>-703</v>
       </c>
     </row>
@@ -2000,15 +2096,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I24" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24">
+        <v>Spend note · Dentist</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Spend note · Dentist | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>-698</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>-698</v>
       </c>
     </row>
@@ -2038,15 +2137,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I25" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25">
+        <v>Spend note · Home goods</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Spend note · Home goods | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25">
         <v>-694</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>-694</v>
       </c>
     </row>
@@ -2076,15 +2178,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I26" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26">
+        <v>Spend note · Takeout</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Spend note · Takeout | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26">
         <v>-689</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>-689</v>
       </c>
     </row>
@@ -2114,15 +2219,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I27" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27">
+        <v>Spend note · Groceries</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Spend note · Groceries | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27">
         <v>-684</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>-684</v>
       </c>
     </row>
@@ -2152,15 +2260,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I28" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28">
+        <v>Spend note · Transit pass</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Spend note · Transit pass | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>-680</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>-680</v>
       </c>
     </row>
@@ -2190,15 +2301,18 @@
         <v/>
       </c>
       <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29">
+        <v>Spend note · Coffee</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Spend note · Coffee</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29">
         <v>-675</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>-675</v>
       </c>
     </row>
@@ -2228,15 +2342,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I30" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30">
+        <v>Spend note · Lunch · reviewed</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Spend note · Lunch · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30">
         <v>-671</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>-671</v>
       </c>
     </row>
@@ -2266,15 +2383,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I31" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31">
+        <v>Spend note · Pharmacy</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Spend note · Pharmacy | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31">
         <v>-666</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>-666</v>
       </c>
     </row>
@@ -2304,15 +2424,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I32" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32">
+        <v>Spend note · Fuel</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Spend note · Fuel | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32">
         <v>-661</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>-661</v>
       </c>
     </row>
@@ -2342,15 +2465,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I33" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J33" t="b">
+        <v>Spend note · Parking</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Spend note · Parking | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K33" t="b">
         <v>1</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>-657</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>-657</v>
       </c>
     </row>
@@ -2380,15 +2506,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I34" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34">
+        <v>Spend note · Dinner</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Spend note · Dinner | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34">
         <v>-652</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>-652</v>
       </c>
     </row>
@@ -2418,15 +2547,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I35" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35">
+        <v>Spend note · Books</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Spend note · Books | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35">
         <v>-647</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>-647</v>
       </c>
     </row>
@@ -2456,15 +2588,18 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v/>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36">
         <v>-643</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>-643</v>
       </c>
     </row>
@@ -2494,15 +2629,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I37" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37">
+        <v>Spend note · Haircut · reviewed</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Spend note · Haircut · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37">
         <v>-638</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>-638</v>
       </c>
     </row>
@@ -2532,15 +2670,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I38" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38">
+        <v>Spend note · Pet supplies</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Spend note · Pet supplies | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38">
         <v>-634</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>-634</v>
       </c>
     </row>
@@ -2570,15 +2711,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I39" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39">
+        <v>Spend note · Gift</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Spend note · Gift | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39">
         <v>-629</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>-629</v>
       </c>
     </row>
@@ -2608,15 +2752,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I40" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J40" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40">
+        <v>Spend note · Train</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Spend note · Train | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40">
         <v>-624</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>-624</v>
       </c>
     </row>
@@ -2646,15 +2793,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I41" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J41" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41">
+        <v>Spend note · Snacks</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Spend note · Snacks | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41">
         <v>-620</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>-620</v>
       </c>
     </row>
@@ -2684,15 +2834,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I42" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42">
+        <v>Spend note · Clothing</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Spend note · Clothing | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42">
         <v>-615</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>-615</v>
       </c>
     </row>
@@ -2722,15 +2875,18 @@
         <v/>
       </c>
       <c r="I43" t="str">
-        <v/>
-      </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43">
+        <v>Spend note · Electronics</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Spend note · Electronics</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43">
         <v>-610</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>-610</v>
       </c>
     </row>
@@ -2760,15 +2916,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I44" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44">
+        <v>Spend note · Movie · reviewed</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Spend note · Movie · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44">
         <v>-606</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>-606</v>
       </c>
     </row>
@@ -2798,15 +2957,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I45" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45">
+        <v>Spend note · Taxi</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Spend note · Taxi | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45">
         <v>-601</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>-601</v>
       </c>
     </row>
@@ -2836,15 +2998,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I46" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46">
+        <v>Spend note · Water bill share</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Spend note · Water bill share | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46">
         <v>-597</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>-597</v>
       </c>
     </row>
@@ -2874,15 +3039,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I47" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47">
+        <v>Spend note · Office supplies</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Spend note · Office supplies | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47">
         <v>-592</v>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>-592</v>
       </c>
     </row>
@@ -2912,15 +3080,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I48" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48">
+        <v>Spend note · Yoga</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Spend note · Yoga | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48">
         <v>-587</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>-587</v>
       </c>
     </row>
@@ -2950,15 +3121,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I49" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49">
+        <v>Spend note · Dentist</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Spend note · Dentist | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49">
         <v>-583</v>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>-583</v>
       </c>
     </row>
@@ -2988,15 +3162,18 @@
         <v/>
       </c>
       <c r="I50" t="str">
-        <v/>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50">
+        <v>Spend note · Home goods</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Spend note · Home goods</v>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50">
         <v>-578</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>-578</v>
       </c>
     </row>
@@ -3026,15 +3203,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I51" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51">
+        <v>Spend note · Takeout · reviewed</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Spend note · Takeout · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51">
         <v>-573</v>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>-573</v>
       </c>
     </row>
@@ -3064,15 +3244,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I52" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52">
+        <v>Spend note · Groceries</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Spend note · Groceries | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52">
         <v>-569</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>-569</v>
       </c>
     </row>
@@ -3102,15 +3285,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I53" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53">
         <v>-564</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>-564</v>
       </c>
     </row>
@@ -3140,15 +3326,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I54" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54">
+        <v>Spend note · Coffee</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Spend note · Coffee | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54">
         <v>-560</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>-560</v>
       </c>
     </row>
@@ -3178,15 +3367,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I55" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55">
+        <v>Spend note · Lunch</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Spend note · Lunch | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55">
         <v>-555</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>-555</v>
       </c>
     </row>
@@ -3216,15 +3408,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I56" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56">
+        <v>Spend note · Pharmacy</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Spend note · Pharmacy | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56">
         <v>-550</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>-550</v>
       </c>
     </row>
@@ -3254,15 +3449,18 @@
         <v/>
       </c>
       <c r="I57" t="str">
-        <v/>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57">
+        <v>Spend note · Fuel</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Spend note · Fuel</v>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57">
         <v>-546</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>-546</v>
       </c>
     </row>
@@ -3292,15 +3490,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I58" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58">
+        <v>Spend note · Parking · reviewed</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Spend note · Parking · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58">
         <v>-541</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>-541</v>
       </c>
     </row>
@@ -3330,15 +3531,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I59" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59">
+        <v>Spend note · Dinner</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Spend note · Dinner | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59">
         <v>-536</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>-536</v>
       </c>
     </row>
@@ -3368,15 +3572,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I60" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60">
+        <v>Spend note · Books</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Spend note · Books | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60">
         <v>-532</v>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>-532</v>
       </c>
     </row>
@@ -3406,15 +3613,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I61" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61">
+        <v>Spend note · Gym</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Spend note · Gym | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61">
         <v>-527</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>-527</v>
       </c>
     </row>
@@ -3444,15 +3654,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I62" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62">
+        <v>Spend note · Haircut</v>
+      </c>
+      <c r="J62" t="str">
+        <v>Spend note · Haircut | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62">
         <v>-523</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>-523</v>
       </c>
     </row>
@@ -3482,15 +3695,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I63" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63">
+        <v>Spend note · Pet supplies</v>
+      </c>
+      <c r="J63" t="str">
+        <v>Spend note · Pet supplies | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63">
         <v>-518</v>
       </c>
-      <c r="L63">
+      <c r="M63">
         <v>-518</v>
       </c>
     </row>
@@ -3520,15 +3736,18 @@
         <v/>
       </c>
       <c r="I64" t="str">
-        <v/>
-      </c>
-      <c r="J64" t="b">
+        <v>Spend note · Gift</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Spend note · Gift</v>
+      </c>
+      <c r="K64" t="b">
         <v>1</v>
       </c>
-      <c r="K64">
+      <c r="L64">
         <v>-513</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>-513</v>
       </c>
     </row>
@@ -3558,15 +3777,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I65" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65">
+        <v>Spend note · Train · reviewed</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Spend note · Train · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65">
         <v>-509</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>-509</v>
       </c>
     </row>
@@ -3596,15 +3818,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I66" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66">
+        <v>Spend note · Snacks</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Spend note · Snacks | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66">
         <v>-504</v>
       </c>
-      <c r="L66">
+      <c r="M66">
         <v>-504</v>
       </c>
     </row>
@@ -3634,15 +3859,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I67" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67">
+        <v>Spend note · Clothing</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Spend note · Clothing | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67">
         <v>-499</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>-499</v>
       </c>
     </row>
@@ -3672,15 +3900,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I68" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68">
+        <v>Spend note · Electronics</v>
+      </c>
+      <c r="J68" t="str">
+        <v>Spend note · Electronics | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68">
         <v>-495</v>
       </c>
-      <c r="L68">
+      <c r="M68">
         <v>-495</v>
       </c>
     </row>
@@ -3710,15 +3941,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I69" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69">
+        <v>Spend note · Movie</v>
+      </c>
+      <c r="J69" t="str">
+        <v>Spend note · Movie | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69">
         <v>-490</v>
       </c>
-      <c r="L69">
+      <c r="M69">
         <v>-490</v>
       </c>
     </row>
@@ -3748,15 +3982,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I70" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J70" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70">
         <v>-486</v>
       </c>
-      <c r="L70">
+      <c r="M70">
         <v>-486</v>
       </c>
     </row>
@@ -3786,15 +4023,18 @@
         <v/>
       </c>
       <c r="I71" t="str">
-        <v/>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71">
+        <v>Spend note · Water bill share</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Spend note · Water bill share</v>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71">
         <v>-481</v>
       </c>
-      <c r="L71">
+      <c r="M71">
         <v>-481</v>
       </c>
     </row>
@@ -3824,15 +4064,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I72" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72">
+        <v>Spend note · Office supplies · reviewed</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Spend note · Office supplies · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72">
         <v>-476</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <v>-476</v>
       </c>
     </row>
@@ -3862,15 +4105,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I73" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73">
+        <v>Spend note · Yoga</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Spend note · Yoga | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73">
         <v>-472</v>
       </c>
-      <c r="L73">
+      <c r="M73">
         <v>-472</v>
       </c>
     </row>
@@ -3900,15 +4146,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I74" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74">
+        <v>Spend note · Dentist</v>
+      </c>
+      <c r="J74" t="str">
+        <v>Spend note · Dentist | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74">
         <v>-467</v>
       </c>
-      <c r="L74">
+      <c r="M74">
         <v>-467</v>
       </c>
     </row>
@@ -3938,15 +4187,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I75" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75">
+        <v>Spend note · Home goods</v>
+      </c>
+      <c r="J75" t="str">
+        <v>Spend note · Home goods | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75">
         <v>-463</v>
       </c>
-      <c r="L75">
+      <c r="M75">
         <v>-463</v>
       </c>
     </row>
@@ -3976,15 +4228,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I76" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76">
+        <v>Spend note · Takeout</v>
+      </c>
+      <c r="J76" t="str">
+        <v>Spend note · Takeout | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76">
         <v>-458</v>
       </c>
-      <c r="L76">
+      <c r="M76">
         <v>-458</v>
       </c>
     </row>
@@ -4014,15 +4269,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I77" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77">
+        <v>Spend note · Groceries</v>
+      </c>
+      <c r="J77" t="str">
+        <v>Spend note · Groceries | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77">
         <v>-453</v>
       </c>
-      <c r="L77">
+      <c r="M77">
         <v>-453</v>
       </c>
     </row>
@@ -4052,15 +4310,18 @@
         <v/>
       </c>
       <c r="I78" t="str">
-        <v/>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78">
+        <v>Spend note · Transit pass</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Spend note · Transit pass</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78">
         <v>-449</v>
       </c>
-      <c r="L78">
+      <c r="M78">
         <v>-449</v>
       </c>
     </row>
@@ -4090,15 +4351,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I79" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79">
+        <v>Spend note · Coffee · reviewed</v>
+      </c>
+      <c r="J79" t="str">
+        <v>Spend note · Coffee · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79">
         <v>-444</v>
       </c>
-      <c r="L79">
+      <c r="M79">
         <v>-444</v>
       </c>
     </row>
@@ -4128,15 +4392,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I80" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80">
+        <v>Spend note · Lunch</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Spend note · Lunch | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80">
         <v>-439</v>
       </c>
-      <c r="L80">
+      <c r="M80">
         <v>-439</v>
       </c>
     </row>
@@ -4166,15 +4433,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I81" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81">
+        <v>Spend note · Pharmacy</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Spend note · Pharmacy | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81">
         <v>-435</v>
       </c>
-      <c r="L81">
+      <c r="M81">
         <v>-435</v>
       </c>
     </row>
@@ -4204,15 +4474,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I82" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82">
+        <v>Spend note · Fuel</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Spend note · Fuel | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82">
         <v>-430</v>
       </c>
-      <c r="L82">
+      <c r="M82">
         <v>-430</v>
       </c>
     </row>
@@ -4242,15 +4515,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I83" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83">
+        <v>Spend note · Parking</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Spend note · Parking | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83">
         <v>-426</v>
       </c>
-      <c r="L83">
+      <c r="M83">
         <v>-426</v>
       </c>
     </row>
@@ -4280,15 +4556,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I84" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84">
+        <v>Spend note · Dinner</v>
+      </c>
+      <c r="J84" t="str">
+        <v>Spend note · Dinner | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84">
         <v>-421</v>
       </c>
-      <c r="L84">
+      <c r="M84">
         <v>-421</v>
       </c>
     </row>
@@ -4318,15 +4597,18 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v/>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85">
+        <v>Spend note · Books</v>
+      </c>
+      <c r="J85" t="str">
+        <v>Spend note · Books</v>
+      </c>
+      <c r="K85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85">
         <v>-416</v>
       </c>
-      <c r="L85">
+      <c r="M85">
         <v>-416</v>
       </c>
     </row>
@@ -4356,15 +4638,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I86" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86">
+        <v>Spend note · Gym · reviewed</v>
+      </c>
+      <c r="J86" t="str">
+        <v>Spend note · Gym · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K86" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86">
         <v>-412</v>
       </c>
-      <c r="L86">
+      <c r="M86">
         <v>-412</v>
       </c>
     </row>
@@ -4394,15 +4679,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I87" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J87" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87">
         <v>-407</v>
       </c>
-      <c r="L87">
+      <c r="M87">
         <v>-407</v>
       </c>
     </row>
@@ -4432,15 +4720,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I88" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J88" t="b">
-        <v>0</v>
-      </c>
-      <c r="K88">
+        <v>Spend note · Pet supplies</v>
+      </c>
+      <c r="J88" t="str">
+        <v>Spend note · Pet supplies | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88">
         <v>-402</v>
       </c>
-      <c r="L88">
+      <c r="M88">
         <v>-402</v>
       </c>
     </row>
@@ -4470,15 +4761,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I89" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J89" t="b">
-        <v>0</v>
-      </c>
-      <c r="K89">
+        <v>Spend note · Gift</v>
+      </c>
+      <c r="J89" t="str">
+        <v>Spend note · Gift | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89">
         <v>-398</v>
       </c>
-      <c r="L89">
+      <c r="M89">
         <v>-398</v>
       </c>
     </row>
@@ -4508,15 +4802,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I90" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J90" t="b">
-        <v>0</v>
-      </c>
-      <c r="K90">
+        <v>Spend note · Train</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Spend note · Train | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K90" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90">
         <v>-393</v>
       </c>
-      <c r="L90">
+      <c r="M90">
         <v>-393</v>
       </c>
     </row>
@@ -4546,15 +4843,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I91" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J91" t="b">
-        <v>0</v>
-      </c>
-      <c r="K91">
+        <v>Spend note · Snacks</v>
+      </c>
+      <c r="J91" t="str">
+        <v>Spend note · Snacks | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K91" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91">
         <v>-389</v>
       </c>
-      <c r="L91">
+      <c r="M91">
         <v>-389</v>
       </c>
     </row>
@@ -4584,15 +4884,18 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v/>
-      </c>
-      <c r="J92" t="b">
-        <v>0</v>
-      </c>
-      <c r="K92">
+        <v>Spend note · Clothing</v>
+      </c>
+      <c r="J92" t="str">
+        <v>Spend note · Clothing</v>
+      </c>
+      <c r="K92" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92">
         <v>-384</v>
       </c>
-      <c r="L92">
+      <c r="M92">
         <v>-384</v>
       </c>
     </row>
@@ -4622,15 +4925,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I93" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J93" t="b">
-        <v>0</v>
-      </c>
-      <c r="K93">
+        <v>Spend note · Electronics · reviewed</v>
+      </c>
+      <c r="J93" t="str">
+        <v>Spend note · Electronics · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K93" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93">
         <v>-379</v>
       </c>
-      <c r="L93">
+      <c r="M93">
         <v>-379</v>
       </c>
     </row>
@@ -4660,15 +4966,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I94" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J94" t="b">
-        <v>0</v>
-      </c>
-      <c r="K94">
+        <v>Spend note · Movie</v>
+      </c>
+      <c r="J94" t="str">
+        <v>Spend note · Movie | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K94" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94">
         <v>-375</v>
       </c>
-      <c r="L94">
+      <c r="M94">
         <v>-375</v>
       </c>
     </row>
@@ -4698,15 +5007,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I95" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J95" t="b">
+        <v>Spend note · Taxi</v>
+      </c>
+      <c r="J95" t="str">
+        <v>Spend note · Taxi | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K95" t="b">
         <v>1</v>
       </c>
-      <c r="K95">
+      <c r="L95">
         <v>-370</v>
       </c>
-      <c r="L95">
+      <c r="M95">
         <v>-370</v>
       </c>
     </row>
@@ -4736,15 +5048,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I96" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J96" t="b">
-        <v>0</v>
-      </c>
-      <c r="K96">
+        <v>Spend note · Water bill share</v>
+      </c>
+      <c r="J96" t="str">
+        <v>Spend note · Water bill share | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K96" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96">
         <v>-365</v>
       </c>
-      <c r="L96">
+      <c r="M96">
         <v>-365</v>
       </c>
     </row>
@@ -4774,15 +5089,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I97" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97">
+        <v>Spend note · Office supplies</v>
+      </c>
+      <c r="J97" t="str">
+        <v>Spend note · Office supplies | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K97" t="b">
+        <v>0</v>
+      </c>
+      <c r="L97">
         <v>-361</v>
       </c>
-      <c r="L97">
+      <c r="M97">
         <v>-361</v>
       </c>
     </row>
@@ -4812,15 +5130,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I98" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98">
+        <v>Spend note · Yoga</v>
+      </c>
+      <c r="J98" t="str">
+        <v>Spend note · Yoga | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K98" t="b">
+        <v>0</v>
+      </c>
+      <c r="L98">
         <v>-356</v>
       </c>
-      <c r="L98">
+      <c r="M98">
         <v>-356</v>
       </c>
     </row>
@@ -4850,15 +5171,18 @@
         <v/>
       </c>
       <c r="I99" t="str">
-        <v/>
-      </c>
-      <c r="J99" t="b">
-        <v>0</v>
-      </c>
-      <c r="K99">
+        <v>Spend note · Dentist</v>
+      </c>
+      <c r="J99" t="str">
+        <v>Spend note · Dentist</v>
+      </c>
+      <c r="K99" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99">
         <v>-352</v>
       </c>
-      <c r="L99">
+      <c r="M99">
         <v>-352</v>
       </c>
     </row>
@@ -4888,15 +5212,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I100" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J100" t="b">
-        <v>0</v>
-      </c>
-      <c r="K100">
+        <v>Spend note · Home goods · reviewed</v>
+      </c>
+      <c r="J100" t="str">
+        <v>Spend note · Home goods · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K100" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100">
         <v>-347</v>
       </c>
-      <c r="L100">
+      <c r="M100">
         <v>-347</v>
       </c>
     </row>
@@ -4926,15 +5253,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I101" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J101" t="b">
-        <v>0</v>
-      </c>
-      <c r="K101">
+        <v>Spend note · Takeout</v>
+      </c>
+      <c r="J101" t="str">
+        <v>Spend note · Takeout | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K101" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101">
         <v>-342</v>
       </c>
-      <c r="L101">
+      <c r="M101">
         <v>-342</v>
       </c>
     </row>
@@ -4964,15 +5294,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I102" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J102" t="b">
-        <v>0</v>
-      </c>
-      <c r="K102">
+        <v>Spend note · Groceries</v>
+      </c>
+      <c r="J102" t="str">
+        <v>Spend note · Groceries | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K102" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102">
         <v>-338</v>
       </c>
-      <c r="L102">
+      <c r="M102">
         <v>-338</v>
       </c>
     </row>
@@ -5002,15 +5335,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I103" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J103" t="b">
-        <v>0</v>
-      </c>
-      <c r="K103">
+        <v>Spend note · Transit pass</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Spend note · Transit pass | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K103" t="b">
+        <v>0</v>
+      </c>
+      <c r="L103">
         <v>-333</v>
       </c>
-      <c r="L103">
+      <c r="M103">
         <v>-333</v>
       </c>
     </row>
@@ -5040,15 +5376,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I104" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J104" t="b">
-        <v>0</v>
-      </c>
-      <c r="K104">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J104" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K104" t="b">
+        <v>0</v>
+      </c>
+      <c r="L104">
         <v>-328</v>
       </c>
-      <c r="L104">
+      <c r="M104">
         <v>-328</v>
       </c>
     </row>
@@ -5078,15 +5417,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I105" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J105" t="b">
-        <v>0</v>
-      </c>
-      <c r="K105">
+        <v>Spend note · Lunch</v>
+      </c>
+      <c r="J105" t="str">
+        <v>Spend note · Lunch | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K105" t="b">
+        <v>0</v>
+      </c>
+      <c r="L105">
         <v>-324</v>
       </c>
-      <c r="L105">
+      <c r="M105">
         <v>-324</v>
       </c>
     </row>
@@ -5116,15 +5458,18 @@
         <v/>
       </c>
       <c r="I106" t="str">
-        <v/>
-      </c>
-      <c r="J106" t="b">
-        <v>0</v>
-      </c>
-      <c r="K106">
+        <v>Spend note · Pharmacy</v>
+      </c>
+      <c r="J106" t="str">
+        <v>Spend note · Pharmacy</v>
+      </c>
+      <c r="K106" t="b">
+        <v>0</v>
+      </c>
+      <c r="L106">
         <v>-319</v>
       </c>
-      <c r="L106">
+      <c r="M106">
         <v>-319</v>
       </c>
     </row>
@@ -5154,15 +5499,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I107" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J107" t="b">
-        <v>0</v>
-      </c>
-      <c r="K107">
+        <v>Spend note · Fuel · reviewed</v>
+      </c>
+      <c r="J107" t="str">
+        <v>Spend note · Fuel · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K107" t="b">
+        <v>0</v>
+      </c>
+      <c r="L107">
         <v>-315</v>
       </c>
-      <c r="L107">
+      <c r="M107">
         <v>-315</v>
       </c>
     </row>
@@ -5192,15 +5540,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I108" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J108" t="b">
-        <v>0</v>
-      </c>
-      <c r="K108">
+        <v>Spend note · Parking</v>
+      </c>
+      <c r="J108" t="str">
+        <v>Spend note · Parking | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K108" t="b">
+        <v>0</v>
+      </c>
+      <c r="L108">
         <v>-310</v>
       </c>
-      <c r="L108">
+      <c r="M108">
         <v>-310</v>
       </c>
     </row>
@@ -5230,15 +5581,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I109" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J109" t="b">
-        <v>0</v>
-      </c>
-      <c r="K109">
+        <v>Spend note · Dinner</v>
+      </c>
+      <c r="J109" t="str">
+        <v>Spend note · Dinner | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K109" t="b">
+        <v>0</v>
+      </c>
+      <c r="L109">
         <v>-305</v>
       </c>
-      <c r="L109">
+      <c r="M109">
         <v>-305</v>
       </c>
     </row>
@@ -5268,15 +5622,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I110" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J110" t="b">
-        <v>0</v>
-      </c>
-      <c r="K110">
+        <v>Spend note · Books</v>
+      </c>
+      <c r="J110" t="str">
+        <v>Spend note · Books | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K110" t="b">
+        <v>0</v>
+      </c>
+      <c r="L110">
         <v>-301</v>
       </c>
-      <c r="L110">
+      <c r="M110">
         <v>-301</v>
       </c>
     </row>
@@ -5306,15 +5663,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I111" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J111" t="b">
-        <v>0</v>
-      </c>
-      <c r="K111">
+        <v>Spend note · Gym</v>
+      </c>
+      <c r="J111" t="str">
+        <v>Spend note · Gym | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K111" t="b">
+        <v>0</v>
+      </c>
+      <c r="L111">
         <v>-296</v>
       </c>
-      <c r="L111">
+      <c r="M111">
         <v>-296</v>
       </c>
     </row>
@@ -5344,15 +5704,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I112" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J112" t="b">
-        <v>0</v>
-      </c>
-      <c r="K112">
+        <v>Spend note · Haircut</v>
+      </c>
+      <c r="J112" t="str">
+        <v>Spend note · Haircut | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K112" t="b">
+        <v>0</v>
+      </c>
+      <c r="L112">
         <v>-291</v>
       </c>
-      <c r="L112">
+      <c r="M112">
         <v>-291</v>
       </c>
     </row>
@@ -5382,15 +5745,18 @@
         <v/>
       </c>
       <c r="I113" t="str">
-        <v/>
-      </c>
-      <c r="J113" t="b">
-        <v>0</v>
-      </c>
-      <c r="K113">
+        <v>Spend note · Pet supplies</v>
+      </c>
+      <c r="J113" t="str">
+        <v>Spend note · Pet supplies</v>
+      </c>
+      <c r="K113" t="b">
+        <v>0</v>
+      </c>
+      <c r="L113">
         <v>-287</v>
       </c>
-      <c r="L113">
+      <c r="M113">
         <v>-287</v>
       </c>
     </row>
@@ -5420,15 +5786,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I114" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J114" t="b">
-        <v>0</v>
-      </c>
-      <c r="K114">
+        <v>Spend note · Gift · reviewed</v>
+      </c>
+      <c r="J114" t="str">
+        <v>Spend note · Gift · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K114" t="b">
+        <v>0</v>
+      </c>
+      <c r="L114">
         <v>-282</v>
       </c>
-      <c r="L114">
+      <c r="M114">
         <v>-282</v>
       </c>
     </row>
@@ -5458,15 +5827,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I115" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J115" t="b">
-        <v>0</v>
-      </c>
-      <c r="K115">
+        <v>Spend note · Train</v>
+      </c>
+      <c r="J115" t="str">
+        <v>Spend note · Train | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K115" t="b">
+        <v>0</v>
+      </c>
+      <c r="L115">
         <v>-278</v>
       </c>
-      <c r="L115">
+      <c r="M115">
         <v>-278</v>
       </c>
     </row>
@@ -5496,15 +5868,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I116" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J116" t="b">
-        <v>0</v>
-      </c>
-      <c r="K116">
+        <v>Spend note · Snacks</v>
+      </c>
+      <c r="J116" t="str">
+        <v>Spend note · Snacks | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K116" t="b">
+        <v>0</v>
+      </c>
+      <c r="L116">
         <v>-273</v>
       </c>
-      <c r="L116">
+      <c r="M116">
         <v>-273</v>
       </c>
     </row>
@@ -5534,15 +5909,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I117" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J117" t="b">
-        <v>0</v>
-      </c>
-      <c r="K117">
+        <v>Spend note · Clothing</v>
+      </c>
+      <c r="J117" t="str">
+        <v>Spend note · Clothing | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K117" t="b">
+        <v>0</v>
+      </c>
+      <c r="L117">
         <v>-268</v>
       </c>
-      <c r="L117">
+      <c r="M117">
         <v>-268</v>
       </c>
     </row>
@@ -5572,15 +5950,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I118" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J118" t="b">
-        <v>0</v>
-      </c>
-      <c r="K118">
+        <v>Spend note · Electronics</v>
+      </c>
+      <c r="J118" t="str">
+        <v>Spend note · Electronics | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K118" t="b">
+        <v>0</v>
+      </c>
+      <c r="L118">
         <v>-264</v>
       </c>
-      <c r="L118">
+      <c r="M118">
         <v>-264</v>
       </c>
     </row>
@@ -5610,15 +5991,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I119" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J119" t="b">
-        <v>0</v>
-      </c>
-      <c r="K119">
+        <v>Spend note · Movie</v>
+      </c>
+      <c r="J119" t="str">
+        <v>Spend note · Movie | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K119" t="b">
+        <v>0</v>
+      </c>
+      <c r="L119">
         <v>-259</v>
       </c>
-      <c r="L119">
+      <c r="M119">
         <v>-259</v>
       </c>
     </row>
@@ -5648,15 +6032,18 @@
         <v/>
       </c>
       <c r="I120" t="str">
-        <v/>
-      </c>
-      <c r="J120" t="b">
-        <v>0</v>
-      </c>
-      <c r="K120">
+        <v>Spend note · Taxi</v>
+      </c>
+      <c r="J120" t="str">
+        <v>Spend note · Taxi</v>
+      </c>
+      <c r="K120" t="b">
+        <v>0</v>
+      </c>
+      <c r="L120">
         <v>-254</v>
       </c>
-      <c r="L120">
+      <c r="M120">
         <v>-254</v>
       </c>
     </row>
@@ -5686,15 +6073,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I121" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J121" t="b">
-        <v>0</v>
-      </c>
-      <c r="K121">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J121" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K121" t="b">
+        <v>0</v>
+      </c>
+      <c r="L121">
         <v>-250</v>
       </c>
-      <c r="L121">
+      <c r="M121">
         <v>-250</v>
       </c>
     </row>
@@ -5724,15 +6114,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I122" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J122" t="b">
-        <v>0</v>
-      </c>
-      <c r="K122">
+        <v>Spend note · Office supplies</v>
+      </c>
+      <c r="J122" t="str">
+        <v>Spend note · Office supplies | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K122" t="b">
+        <v>0</v>
+      </c>
+      <c r="L122">
         <v>-245</v>
       </c>
-      <c r="L122">
+      <c r="M122">
         <v>-245</v>
       </c>
     </row>
@@ -5762,15 +6155,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I123" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J123" t="b">
-        <v>0</v>
-      </c>
-      <c r="K123">
+        <v>Spend note · Yoga</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Spend note · Yoga | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K123" t="b">
+        <v>0</v>
+      </c>
+      <c r="L123">
         <v>-241</v>
       </c>
-      <c r="L123">
+      <c r="M123">
         <v>-241</v>
       </c>
     </row>
@@ -5800,15 +6196,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I124" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J124" t="b">
-        <v>0</v>
-      </c>
-      <c r="K124">
+        <v>Spend note · Dentist</v>
+      </c>
+      <c r="J124" t="str">
+        <v>Spend note · Dentist | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K124" t="b">
+        <v>0</v>
+      </c>
+      <c r="L124">
         <v>-236</v>
       </c>
-      <c r="L124">
+      <c r="M124">
         <v>-236</v>
       </c>
     </row>
@@ -5838,15 +6237,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I125" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J125" t="b">
-        <v>0</v>
-      </c>
-      <c r="K125">
+        <v>Spend note · Home goods</v>
+      </c>
+      <c r="J125" t="str">
+        <v>Spend note · Home goods | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K125" t="b">
+        <v>0</v>
+      </c>
+      <c r="L125">
         <v>-231</v>
       </c>
-      <c r="L125">
+      <c r="M125">
         <v>-231</v>
       </c>
     </row>
@@ -5876,15 +6278,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I126" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J126" t="b">
+        <v>Spend note · Takeout</v>
+      </c>
+      <c r="J126" t="str">
+        <v>Spend note · Takeout | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K126" t="b">
         <v>1</v>
       </c>
-      <c r="K126">
+      <c r="L126">
         <v>-227</v>
       </c>
-      <c r="L126">
+      <c r="M126">
         <v>-227</v>
       </c>
     </row>
@@ -5914,15 +6319,18 @@
         <v/>
       </c>
       <c r="I127" t="str">
-        <v/>
-      </c>
-      <c r="J127" t="b">
-        <v>0</v>
-      </c>
-      <c r="K127">
+        <v>Spend note · Groceries</v>
+      </c>
+      <c r="J127" t="str">
+        <v>Spend note · Groceries</v>
+      </c>
+      <c r="K127" t="b">
+        <v>0</v>
+      </c>
+      <c r="L127">
         <v>-222</v>
       </c>
-      <c r="L127">
+      <c r="M127">
         <v>-222</v>
       </c>
     </row>
@@ -5952,15 +6360,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I128" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J128" t="b">
-        <v>0</v>
-      </c>
-      <c r="K128">
+        <v>Spend note · Transit pass · reviewed</v>
+      </c>
+      <c r="J128" t="str">
+        <v>Spend note · Transit pass · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K128" t="b">
+        <v>0</v>
+      </c>
+      <c r="L128">
         <v>-217</v>
       </c>
-      <c r="L128">
+      <c r="M128">
         <v>-217</v>
       </c>
     </row>
@@ -5990,15 +6401,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I129" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J129" t="b">
-        <v>0</v>
-      </c>
-      <c r="K129">
+        <v>Spend note · Coffee</v>
+      </c>
+      <c r="J129" t="str">
+        <v>Spend note · Coffee | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L129">
         <v>-213</v>
       </c>
-      <c r="L129">
+      <c r="M129">
         <v>-213</v>
       </c>
     </row>
@@ -6028,15 +6442,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I130" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J130" t="b">
-        <v>0</v>
-      </c>
-      <c r="K130">
+        <v>Spend note · Lunch</v>
+      </c>
+      <c r="J130" t="str">
+        <v>Spend note · Lunch | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K130" t="b">
+        <v>0</v>
+      </c>
+      <c r="L130">
         <v>-208</v>
       </c>
-      <c r="L130">
+      <c r="M130">
         <v>-208</v>
       </c>
     </row>
@@ -6066,15 +6483,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I131" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J131" t="b">
-        <v>0</v>
-      </c>
-      <c r="K131">
+        <v>Spend note · Pharmacy</v>
+      </c>
+      <c r="J131" t="str">
+        <v>Spend note · Pharmacy | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K131" t="b">
+        <v>0</v>
+      </c>
+      <c r="L131">
         <v>-204</v>
       </c>
-      <c r="L131">
+      <c r="M131">
         <v>-204</v>
       </c>
     </row>
@@ -6104,15 +6524,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I132" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J132" t="b">
-        <v>0</v>
-      </c>
-      <c r="K132">
+        <v>Spend note · Fuel</v>
+      </c>
+      <c r="J132" t="str">
+        <v>Spend note · Fuel | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K132" t="b">
+        <v>0</v>
+      </c>
+      <c r="L132">
         <v>-199</v>
       </c>
-      <c r="L132">
+      <c r="M132">
         <v>-199</v>
       </c>
     </row>
@@ -6142,15 +6565,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I133" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J133" t="b">
-        <v>0</v>
-      </c>
-      <c r="K133">
+        <v>Spend note · Parking</v>
+      </c>
+      <c r="J133" t="str">
+        <v>Spend note · Parking | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K133" t="b">
+        <v>0</v>
+      </c>
+      <c r="L133">
         <v>-194</v>
       </c>
-      <c r="L133">
+      <c r="M133">
         <v>-194</v>
       </c>
     </row>
@@ -6180,15 +6606,18 @@
         <v/>
       </c>
       <c r="I134" t="str">
-        <v/>
-      </c>
-      <c r="J134" t="b">
-        <v>0</v>
-      </c>
-      <c r="K134">
+        <v>Spend note · Dinner</v>
+      </c>
+      <c r="J134" t="str">
+        <v>Spend note · Dinner</v>
+      </c>
+      <c r="K134" t="b">
+        <v>0</v>
+      </c>
+      <c r="L134">
         <v>-190</v>
       </c>
-      <c r="L134">
+      <c r="M134">
         <v>-190</v>
       </c>
     </row>
@@ -6218,15 +6647,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I135" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J135" t="b">
-        <v>0</v>
-      </c>
-      <c r="K135">
+        <v>Spend note · Books · reviewed</v>
+      </c>
+      <c r="J135" t="str">
+        <v>Spend note · Books · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K135" t="b">
+        <v>0</v>
+      </c>
+      <c r="L135">
         <v>-185</v>
       </c>
-      <c r="L135">
+      <c r="M135">
         <v>-185</v>
       </c>
     </row>
@@ -6256,15 +6688,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I136" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J136" t="b">
-        <v>0</v>
-      </c>
-      <c r="K136">
+        <v>Spend note · Gym</v>
+      </c>
+      <c r="J136" t="str">
+        <v>Spend note · Gym | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K136" t="b">
+        <v>0</v>
+      </c>
+      <c r="L136">
         <v>-181</v>
       </c>
-      <c r="L136">
+      <c r="M136">
         <v>-181</v>
       </c>
     </row>
@@ -6294,15 +6729,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I137" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J137" t="b">
-        <v>0</v>
-      </c>
-      <c r="K137">
+        <v>Spend note · Haircut</v>
+      </c>
+      <c r="J137" t="str">
+        <v>Spend note · Haircut | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K137" t="b">
+        <v>0</v>
+      </c>
+      <c r="L137">
         <v>-176</v>
       </c>
-      <c r="L137">
+      <c r="M137">
         <v>-176</v>
       </c>
     </row>
@@ -6332,15 +6770,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I138" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J138" t="b">
-        <v>0</v>
-      </c>
-      <c r="K138">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J138" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K138" t="b">
+        <v>0</v>
+      </c>
+      <c r="L138">
         <v>-171</v>
       </c>
-      <c r="L138">
+      <c r="M138">
         <v>-171</v>
       </c>
     </row>
@@ -6370,15 +6811,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I139" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J139" t="b">
-        <v>0</v>
-      </c>
-      <c r="K139">
+        <v>Spend note · Gift</v>
+      </c>
+      <c r="J139" t="str">
+        <v>Spend note · Gift | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K139" t="b">
+        <v>0</v>
+      </c>
+      <c r="L139">
         <v>-167</v>
       </c>
-      <c r="L139">
+      <c r="M139">
         <v>-167</v>
       </c>
     </row>
@@ -6408,15 +6852,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I140" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J140" t="b">
-        <v>0</v>
-      </c>
-      <c r="K140">
+        <v>Spend note · Train</v>
+      </c>
+      <c r="J140" t="str">
+        <v>Spend note · Train | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K140" t="b">
+        <v>0</v>
+      </c>
+      <c r="L140">
         <v>-162</v>
       </c>
-      <c r="L140">
+      <c r="M140">
         <v>-162</v>
       </c>
     </row>
@@ -6446,15 +6893,18 @@
         <v/>
       </c>
       <c r="I141" t="str">
-        <v/>
-      </c>
-      <c r="J141" t="b">
-        <v>0</v>
-      </c>
-      <c r="K141">
+        <v>Spend note · Snacks</v>
+      </c>
+      <c r="J141" t="str">
+        <v>Spend note · Snacks</v>
+      </c>
+      <c r="K141" t="b">
+        <v>0</v>
+      </c>
+      <c r="L141">
         <v>-157</v>
       </c>
-      <c r="L141">
+      <c r="M141">
         <v>-157</v>
       </c>
     </row>
@@ -6484,15 +6934,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I142" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J142" t="b">
-        <v>0</v>
-      </c>
-      <c r="K142">
+        <v>Spend note · Clothing · reviewed</v>
+      </c>
+      <c r="J142" t="str">
+        <v>Spend note · Clothing · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K142" t="b">
+        <v>0</v>
+      </c>
+      <c r="L142">
         <v>-153</v>
       </c>
-      <c r="L142">
+      <c r="M142">
         <v>-153</v>
       </c>
     </row>
@@ -6522,15 +6975,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I143" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J143" t="b">
-        <v>0</v>
-      </c>
-      <c r="K143">
+        <v>Spend note · Electronics</v>
+      </c>
+      <c r="J143" t="str">
+        <v>Spend note · Electronics | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K143" t="b">
+        <v>0</v>
+      </c>
+      <c r="L143">
         <v>-148</v>
       </c>
-      <c r="L143">
+      <c r="M143">
         <v>-148</v>
       </c>
     </row>
@@ -6560,15 +7016,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I144" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J144" t="b">
-        <v>0</v>
-      </c>
-      <c r="K144">
+        <v>Spend note · Movie</v>
+      </c>
+      <c r="J144" t="str">
+        <v>Spend note · Movie | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K144" t="b">
+        <v>0</v>
+      </c>
+      <c r="L144">
         <v>-144</v>
       </c>
-      <c r="L144">
+      <c r="M144">
         <v>-144</v>
       </c>
     </row>
@@ -6598,15 +7057,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I145" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J145" t="b">
-        <v>0</v>
-      </c>
-      <c r="K145">
+        <v>Spend note · Taxi</v>
+      </c>
+      <c r="J145" t="str">
+        <v>Spend note · Taxi | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K145" t="b">
+        <v>0</v>
+      </c>
+      <c r="L145">
         <v>-139</v>
       </c>
-      <c r="L145">
+      <c r="M145">
         <v>-139</v>
       </c>
     </row>
@@ -6636,15 +7098,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I146" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J146" t="b">
-        <v>0</v>
-      </c>
-      <c r="K146">
+        <v>Spend note · Water bill share</v>
+      </c>
+      <c r="J146" t="str">
+        <v>Spend note · Water bill share | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K146" t="b">
+        <v>0</v>
+      </c>
+      <c r="L146">
         <v>-134</v>
       </c>
-      <c r="L146">
+      <c r="M146">
         <v>-134</v>
       </c>
     </row>
@@ -6674,15 +7139,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I147" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J147" t="b">
-        <v>0</v>
-      </c>
-      <c r="K147">
+        <v>Spend note · Office supplies</v>
+      </c>
+      <c r="J147" t="str">
+        <v>Spend note · Office supplies | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K147" t="b">
+        <v>0</v>
+      </c>
+      <c r="L147">
         <v>-130</v>
       </c>
-      <c r="L147">
+      <c r="M147">
         <v>-130</v>
       </c>
     </row>
@@ -6712,15 +7180,18 @@
         <v/>
       </c>
       <c r="I148" t="str">
-        <v/>
-      </c>
-      <c r="J148" t="b">
-        <v>0</v>
-      </c>
-      <c r="K148">
+        <v>Spend note · Yoga</v>
+      </c>
+      <c r="J148" t="str">
+        <v>Spend note · Yoga</v>
+      </c>
+      <c r="K148" t="b">
+        <v>0</v>
+      </c>
+      <c r="L148">
         <v>-125</v>
       </c>
-      <c r="L148">
+      <c r="M148">
         <v>-125</v>
       </c>
     </row>
@@ -6750,15 +7221,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I149" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J149" t="b">
-        <v>0</v>
-      </c>
-      <c r="K149">
+        <v>Spend note · Dentist · reviewed</v>
+      </c>
+      <c r="J149" t="str">
+        <v>Spend note · Dentist · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K149" t="b">
+        <v>0</v>
+      </c>
+      <c r="L149">
         <v>-120</v>
       </c>
-      <c r="L149">
+      <c r="M149">
         <v>-120</v>
       </c>
     </row>
@@ -6788,15 +7262,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I150" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J150" t="b">
-        <v>0</v>
-      </c>
-      <c r="K150">
+        <v>Spend note · Home goods</v>
+      </c>
+      <c r="J150" t="str">
+        <v>Spend note · Home goods | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K150" t="b">
+        <v>0</v>
+      </c>
+      <c r="L150">
         <v>-116</v>
       </c>
-      <c r="L150">
+      <c r="M150">
         <v>-116</v>
       </c>
     </row>
@@ -6826,15 +7303,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I151" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J151" t="b">
-        <v>0</v>
-      </c>
-      <c r="K151">
+        <v>Spend note · Takeout</v>
+      </c>
+      <c r="J151" t="str">
+        <v>Spend note · Takeout | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K151" t="b">
+        <v>0</v>
+      </c>
+      <c r="L151">
         <v>-111</v>
       </c>
-      <c r="L151">
+      <c r="M151">
         <v>-111</v>
       </c>
     </row>
@@ -6864,15 +7344,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I152" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J152" t="b">
-        <v>0</v>
-      </c>
-      <c r="K152">
+        <v>Spend note · Groceries</v>
+      </c>
+      <c r="J152" t="str">
+        <v>Spend note · Groceries | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K152" t="b">
+        <v>0</v>
+      </c>
+      <c r="L152">
         <v>-107</v>
       </c>
-      <c r="L152">
+      <c r="M152">
         <v>-107</v>
       </c>
     </row>
@@ -6902,15 +7385,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I153" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J153" t="b">
-        <v>0</v>
-      </c>
-      <c r="K153">
+        <v>Spend note · Transit pass</v>
+      </c>
+      <c r="J153" t="str">
+        <v>Spend note · Transit pass | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K153" t="b">
+        <v>0</v>
+      </c>
+      <c r="L153">
         <v>-102</v>
       </c>
-      <c r="L153">
+      <c r="M153">
         <v>-102</v>
       </c>
     </row>
@@ -6940,15 +7426,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I154" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J154" t="b">
-        <v>0</v>
-      </c>
-      <c r="K154">
+        <v>Spend note · Coffee</v>
+      </c>
+      <c r="J154" t="str">
+        <v>Spend note · Coffee | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K154" t="b">
+        <v>0</v>
+      </c>
+      <c r="L154">
         <v>-97</v>
       </c>
-      <c r="L154">
+      <c r="M154">
         <v>-97</v>
       </c>
     </row>
@@ -6978,15 +7467,18 @@
         <v/>
       </c>
       <c r="I155" t="str">
-        <v/>
-      </c>
-      <c r="J155" t="b">
-        <v>0</v>
-      </c>
-      <c r="K155">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J155" t="str">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="K155" t="b">
+        <v>0</v>
+      </c>
+      <c r="L155">
         <v>-93</v>
       </c>
-      <c r="L155">
+      <c r="M155">
         <v>-93</v>
       </c>
     </row>
@@ -7016,15 +7508,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I156" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J156" t="b">
-        <v>0</v>
-      </c>
-      <c r="K156">
+        <v>Spend note · Pharmacy · reviewed</v>
+      </c>
+      <c r="J156" t="str">
+        <v>Spend note · Pharmacy · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K156" t="b">
+        <v>0</v>
+      </c>
+      <c r="L156">
         <v>-88</v>
       </c>
-      <c r="L156">
+      <c r="M156">
         <v>-88</v>
       </c>
     </row>
@@ -7054,15 +7549,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I157" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J157" t="b">
+        <v>Spend note · Fuel</v>
+      </c>
+      <c r="J157" t="str">
+        <v>Spend note · Fuel | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K157" t="b">
         <v>1</v>
       </c>
-      <c r="K157">
+      <c r="L157">
         <v>-83</v>
       </c>
-      <c r="L157">
+      <c r="M157">
         <v>-83</v>
       </c>
     </row>
@@ -7092,15 +7590,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I158" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J158" t="b">
-        <v>0</v>
-      </c>
-      <c r="K158">
+        <v>Spend note · Parking</v>
+      </c>
+      <c r="J158" t="str">
+        <v>Spend note · Parking | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K158" t="b">
+        <v>0</v>
+      </c>
+      <c r="L158">
         <v>-79</v>
       </c>
-      <c r="L158">
+      <c r="M158">
         <v>-79</v>
       </c>
     </row>
@@ -7130,15 +7631,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I159" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J159" t="b">
-        <v>0</v>
-      </c>
-      <c r="K159">
+        <v>Spend note · Dinner</v>
+      </c>
+      <c r="J159" t="str">
+        <v>Spend note · Dinner | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K159" t="b">
+        <v>0</v>
+      </c>
+      <c r="L159">
         <v>-74</v>
       </c>
-      <c r="L159">
+      <c r="M159">
         <v>-74</v>
       </c>
     </row>
@@ -7168,15 +7672,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I160" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J160" t="b">
-        <v>0</v>
-      </c>
-      <c r="K160">
+        <v>Spend note · Books</v>
+      </c>
+      <c r="J160" t="str">
+        <v>Spend note · Books | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K160" t="b">
+        <v>0</v>
+      </c>
+      <c r="L160">
         <v>-70</v>
       </c>
-      <c r="L160">
+      <c r="M160">
         <v>-70</v>
       </c>
     </row>
@@ -7206,15 +7713,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I161" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J161" t="b">
-        <v>0</v>
-      </c>
-      <c r="K161">
+        <v>Spend note · Gym</v>
+      </c>
+      <c r="J161" t="str">
+        <v>Spend note · Gym | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K161" t="b">
+        <v>0</v>
+      </c>
+      <c r="L161">
         <v>-65</v>
       </c>
-      <c r="L161">
+      <c r="M161">
         <v>-65</v>
       </c>
     </row>
@@ -7244,15 +7754,18 @@
         <v/>
       </c>
       <c r="I162" t="str">
-        <v/>
-      </c>
-      <c r="J162" t="b">
-        <v>0</v>
-      </c>
-      <c r="K162">
+        <v>Spend note · Haircut</v>
+      </c>
+      <c r="J162" t="str">
+        <v>Spend note · Haircut</v>
+      </c>
+      <c r="K162" t="b">
+        <v>0</v>
+      </c>
+      <c r="L162">
         <v>-60</v>
       </c>
-      <c r="L162">
+      <c r="M162">
         <v>-60</v>
       </c>
     </row>
@@ -7282,15 +7795,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I163" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J163" t="b">
-        <v>0</v>
-      </c>
-      <c r="K163">
+        <v>Spend note · Pet supplies · reviewed</v>
+      </c>
+      <c r="J163" t="str">
+        <v>Spend note · Pet supplies · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K163" t="b">
+        <v>0</v>
+      </c>
+      <c r="L163">
         <v>-56</v>
       </c>
-      <c r="L163">
+      <c r="M163">
         <v>-56</v>
       </c>
     </row>
@@ -7320,15 +7836,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I164" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J164" t="b">
-        <v>0</v>
-      </c>
-      <c r="K164">
+        <v>Spend note · Gift</v>
+      </c>
+      <c r="J164" t="str">
+        <v>Spend note · Gift | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K164" t="b">
+        <v>0</v>
+      </c>
+      <c r="L164">
         <v>-51</v>
       </c>
-      <c r="L164">
+      <c r="M164">
         <v>-51</v>
       </c>
     </row>
@@ -7358,15 +7877,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I165" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J165" t="b">
-        <v>0</v>
-      </c>
-      <c r="K165">
+        <v>Spend note · Train</v>
+      </c>
+      <c r="J165" t="str">
+        <v>Spend note · Train | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K165" t="b">
+        <v>0</v>
+      </c>
+      <c r="L165">
         <v>-46</v>
       </c>
-      <c r="L165">
+      <c r="M165">
         <v>-46</v>
       </c>
     </row>
@@ -7396,15 +7918,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I166" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J166" t="b">
-        <v>0</v>
-      </c>
-      <c r="K166">
+        <v>Spend note · Snacks</v>
+      </c>
+      <c r="J166" t="str">
+        <v>Spend note · Snacks | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K166" t="b">
+        <v>0</v>
+      </c>
+      <c r="L166">
         <v>-42</v>
       </c>
-      <c r="L166">
+      <c r="M166">
         <v>-42</v>
       </c>
     </row>
@@ -7434,15 +7959,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I167" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J167" t="b">
-        <v>0</v>
-      </c>
-      <c r="K167">
+        <v>Spend note · Clothing</v>
+      </c>
+      <c r="J167" t="str">
+        <v>Spend note · Clothing | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K167" t="b">
+        <v>0</v>
+      </c>
+      <c r="L167">
         <v>-37</v>
       </c>
-      <c r="L167">
+      <c r="M167">
         <v>-37</v>
       </c>
     </row>
@@ -7472,15 +8000,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I168" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J168" t="b">
-        <v>0</v>
-      </c>
-      <c r="K168">
+        <v>Spend note · Electronics</v>
+      </c>
+      <c r="J168" t="str">
+        <v>Spend note · Electronics | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K168" t="b">
+        <v>0</v>
+      </c>
+      <c r="L168">
         <v>-33</v>
       </c>
-      <c r="L168">
+      <c r="M168">
         <v>-33</v>
       </c>
     </row>
@@ -7510,15 +8041,18 @@
         <v/>
       </c>
       <c r="I169" t="str">
-        <v/>
-      </c>
-      <c r="J169" t="b">
-        <v>0</v>
-      </c>
-      <c r="K169">
+        <v>Spend note · Movie</v>
+      </c>
+      <c r="J169" t="str">
+        <v>Spend note · Movie</v>
+      </c>
+      <c r="K169" t="b">
+        <v>0</v>
+      </c>
+      <c r="L169">
         <v>-28</v>
       </c>
-      <c r="L169">
+      <c r="M169">
         <v>-28</v>
       </c>
     </row>
@@ -7548,15 +8082,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I170" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J170" t="b">
-        <v>0</v>
-      </c>
-      <c r="K170">
+        <v>Spend note · Taxi · reviewed</v>
+      </c>
+      <c r="J170" t="str">
+        <v>Spend note · Taxi · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K170" t="b">
+        <v>0</v>
+      </c>
+      <c r="L170">
         <v>-23</v>
       </c>
-      <c r="L170">
+      <c r="M170">
         <v>-23</v>
       </c>
     </row>
@@ -7586,15 +8123,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I171" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J171" t="b">
-        <v>0</v>
-      </c>
-      <c r="K171">
+        <v>Spend note · Water bill share</v>
+      </c>
+      <c r="J171" t="str">
+        <v>Spend note · Water bill share | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K171" t="b">
+        <v>0</v>
+      </c>
+      <c r="L171">
         <v>-19</v>
       </c>
-      <c r="L171">
+      <c r="M171">
         <v>-19</v>
       </c>
     </row>
@@ -7624,15 +8164,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I172" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J172" t="b">
-        <v>0</v>
-      </c>
-      <c r="K172">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J172" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K172" t="b">
+        <v>0</v>
+      </c>
+      <c r="L172">
         <v>-14</v>
       </c>
-      <c r="L172">
+      <c r="M172">
         <v>-14</v>
       </c>
     </row>
@@ -7662,15 +8205,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I173" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J173" t="b">
-        <v>0</v>
-      </c>
-      <c r="K173">
+        <v>Spend note · Yoga</v>
+      </c>
+      <c r="J173" t="str">
+        <v>Spend note · Yoga | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K173" t="b">
+        <v>0</v>
+      </c>
+      <c r="L173">
         <v>-9</v>
       </c>
-      <c r="L173">
+      <c r="M173">
         <v>-9</v>
       </c>
     </row>
@@ -7700,15 +8246,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I174" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J174" t="b">
-        <v>0</v>
-      </c>
-      <c r="K174">
+        <v>Spend note · Dentist</v>
+      </c>
+      <c r="J174" t="str">
+        <v>Spend note · Dentist | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K174" t="b">
+        <v>0</v>
+      </c>
+      <c r="L174">
         <v>-5</v>
       </c>
-      <c r="L174">
+      <c r="M174">
         <v>-5</v>
       </c>
     </row>
@@ -7738,15 +8287,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I175" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J175" t="b">
-        <v>0</v>
-      </c>
-      <c r="K175">
+        <v>Spend note · Home goods</v>
+      </c>
+      <c r="J175" t="str">
+        <v>Spend note · Home goods | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K175" t="b">
         <v>0</v>
       </c>
       <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175">
         <v>0</v>
       </c>
     </row>
@@ -7776,15 +8328,18 @@
         <v/>
       </c>
       <c r="I176" t="str">
-        <v/>
-      </c>
-      <c r="J176" t="b">
-        <v>0</v>
-      </c>
-      <c r="K176">
+        <v>Spend note · Takeout</v>
+      </c>
+      <c r="J176" t="str">
+        <v>Spend note · Takeout</v>
+      </c>
+      <c r="K176" t="b">
+        <v>0</v>
+      </c>
+      <c r="L176">
         <v>4</v>
       </c>
-      <c r="L176">
+      <c r="M176">
         <v>4</v>
       </c>
     </row>
@@ -7814,15 +8369,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I177" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J177" t="b">
-        <v>0</v>
-      </c>
-      <c r="K177">
+        <v>Spend note · Groceries · reviewed</v>
+      </c>
+      <c r="J177" t="str">
+        <v>Spend note · Groceries · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K177" t="b">
+        <v>0</v>
+      </c>
+      <c r="L177">
         <v>9</v>
       </c>
-      <c r="L177">
+      <c r="M177">
         <v>9</v>
       </c>
     </row>
@@ -7852,15 +8410,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I178" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J178" t="b">
-        <v>0</v>
-      </c>
-      <c r="K178">
+        <v>Spend note · Transit pass</v>
+      </c>
+      <c r="J178" t="str">
+        <v>Spend note · Transit pass | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K178" t="b">
+        <v>0</v>
+      </c>
+      <c r="L178">
         <v>14</v>
       </c>
-      <c r="L178">
+      <c r="M178">
         <v>14</v>
       </c>
     </row>
@@ -7890,15 +8451,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I179" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J179" t="b">
-        <v>0</v>
-      </c>
-      <c r="K179">
+        <v>Spend note · Coffee</v>
+      </c>
+      <c r="J179" t="str">
+        <v>Spend note · Coffee | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K179" t="b">
+        <v>0</v>
+      </c>
+      <c r="L179">
         <v>18</v>
       </c>
-      <c r="L179">
+      <c r="M179">
         <v>18</v>
       </c>
     </row>
@@ -7928,15 +8492,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I180" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J180" t="b">
-        <v>0</v>
-      </c>
-      <c r="K180">
+        <v>Spend note · Lunch</v>
+      </c>
+      <c r="J180" t="str">
+        <v>Spend note · Lunch | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K180" t="b">
+        <v>0</v>
+      </c>
+      <c r="L180">
         <v>23</v>
       </c>
-      <c r="L180">
+      <c r="M180">
         <v>23</v>
       </c>
     </row>
@@ -7966,15 +8533,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I181" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J181" t="b">
-        <v>0</v>
-      </c>
-      <c r="K181">
+        <v>Spend note · Pharmacy</v>
+      </c>
+      <c r="J181" t="str">
+        <v>Spend note · Pharmacy | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K181" t="b">
+        <v>0</v>
+      </c>
+      <c r="L181">
         <v>28</v>
       </c>
-      <c r="L181">
+      <c r="M181">
         <v>28</v>
       </c>
     </row>
@@ -8004,15 +8574,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I182" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J182" t="b">
-        <v>0</v>
-      </c>
-      <c r="K182">
+        <v>Spend note · Fuel</v>
+      </c>
+      <c r="J182" t="str">
+        <v>Spend note · Fuel | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K182" t="b">
+        <v>0</v>
+      </c>
+      <c r="L182">
         <v>32</v>
       </c>
-      <c r="L182">
+      <c r="M182">
         <v>32</v>
       </c>
     </row>
@@ -8042,15 +8615,18 @@
         <v/>
       </c>
       <c r="I183" t="str">
-        <v/>
-      </c>
-      <c r="J183" t="b">
-        <v>0</v>
-      </c>
-      <c r="K183">
+        <v>Spend note · Parking</v>
+      </c>
+      <c r="J183" t="str">
+        <v>Spend note · Parking</v>
+      </c>
+      <c r="K183" t="b">
+        <v>0</v>
+      </c>
+      <c r="L183">
         <v>37</v>
       </c>
-      <c r="L183">
+      <c r="M183">
         <v>37</v>
       </c>
     </row>
@@ -8080,15 +8656,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I184" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J184" t="b">
-        <v>0</v>
-      </c>
-      <c r="K184">
+        <v>Spend note · Dinner · reviewed</v>
+      </c>
+      <c r="J184" t="str">
+        <v>Spend note · Dinner · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K184" t="b">
+        <v>0</v>
+      </c>
+      <c r="L184">
         <v>41</v>
       </c>
-      <c r="L184">
+      <c r="M184">
         <v>41</v>
       </c>
     </row>
@@ -8118,15 +8697,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I185" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J185" t="b">
-        <v>0</v>
-      </c>
-      <c r="K185">
+        <v>Spend note · Books</v>
+      </c>
+      <c r="J185" t="str">
+        <v>Spend note · Books | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K185" t="b">
+        <v>0</v>
+      </c>
+      <c r="L185">
         <v>46</v>
       </c>
-      <c r="L185">
+      <c r="M185">
         <v>46</v>
       </c>
     </row>
@@ -8156,15 +8738,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I186" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J186" t="b">
-        <v>0</v>
-      </c>
-      <c r="K186">
+        <v>Spend note · Gym</v>
+      </c>
+      <c r="J186" t="str">
+        <v>Spend note · Gym | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K186" t="b">
+        <v>0</v>
+      </c>
+      <c r="L186">
         <v>51</v>
       </c>
-      <c r="L186">
+      <c r="M186">
         <v>51</v>
       </c>
     </row>
@@ -8194,15 +8779,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I187" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J187" t="b">
-        <v>0</v>
-      </c>
-      <c r="K187">
+        <v>Spend note · Haircut</v>
+      </c>
+      <c r="J187" t="str">
+        <v>Spend note · Haircut | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K187" t="b">
+        <v>0</v>
+      </c>
+      <c r="L187">
         <v>55</v>
       </c>
-      <c r="L187">
+      <c r="M187">
         <v>55</v>
       </c>
     </row>
@@ -8232,15 +8820,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I188" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J188" t="b">
+        <v>Spend note · Pet supplies</v>
+      </c>
+      <c r="J188" t="str">
+        <v>Spend note · Pet supplies | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K188" t="b">
         <v>1</v>
       </c>
-      <c r="K188">
+      <c r="L188">
         <v>60</v>
       </c>
-      <c r="L188">
+      <c r="M188">
         <v>60</v>
       </c>
     </row>
@@ -8270,15 +8861,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I189" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J189" t="b">
-        <v>0</v>
-      </c>
-      <c r="K189">
+        <v>Recorded income / credit</v>
+      </c>
+      <c r="J189" t="str">
+        <v>Recorded income / credit | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K189" t="b">
+        <v>0</v>
+      </c>
+      <c r="L189">
         <v>65</v>
       </c>
-      <c r="L189">
+      <c r="M189">
         <v>65</v>
       </c>
     </row>
@@ -8308,15 +8902,18 @@
         <v/>
       </c>
       <c r="I190" t="str">
-        <v/>
-      </c>
-      <c r="J190" t="b">
-        <v>0</v>
-      </c>
-      <c r="K190">
+        <v>Spend note · Train</v>
+      </c>
+      <c r="J190" t="str">
+        <v>Spend note · Train</v>
+      </c>
+      <c r="K190" t="b">
+        <v>0</v>
+      </c>
+      <c r="L190">
         <v>69</v>
       </c>
-      <c r="L190">
+      <c r="M190">
         <v>69</v>
       </c>
     </row>
@@ -8346,15 +8943,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I191" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J191" t="b">
-        <v>0</v>
-      </c>
-      <c r="K191">
+        <v>Spend note · Snacks · reviewed</v>
+      </c>
+      <c r="J191" t="str">
+        <v>Spend note · Snacks · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K191" t="b">
+        <v>0</v>
+      </c>
+      <c r="L191">
         <v>74</v>
       </c>
-      <c r="L191">
+      <c r="M191">
         <v>74</v>
       </c>
     </row>
@@ -8384,15 +8984,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I192" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J192" t="b">
-        <v>0</v>
-      </c>
-      <c r="K192">
+        <v>Spend note · Clothing</v>
+      </c>
+      <c r="J192" t="str">
+        <v>Spend note · Clothing | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K192" t="b">
+        <v>0</v>
+      </c>
+      <c r="L192">
         <v>78</v>
       </c>
-      <c r="L192">
+      <c r="M192">
         <v>78</v>
       </c>
     </row>
@@ -8422,15 +9025,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I193" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J193" t="b">
-        <v>0</v>
-      </c>
-      <c r="K193">
+        <v>Spend note · Electronics</v>
+      </c>
+      <c r="J193" t="str">
+        <v>Spend note · Electronics | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K193" t="b">
+        <v>0</v>
+      </c>
+      <c r="L193">
         <v>83</v>
       </c>
-      <c r="L193">
+      <c r="M193">
         <v>83</v>
       </c>
     </row>
@@ -8460,15 +9066,18 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I194" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J194" t="b">
-        <v>0</v>
-      </c>
-      <c r="K194">
+        <v>Spend note · Movie</v>
+      </c>
+      <c r="J194" t="str">
+        <v>Spend note · Movie | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K194" t="b">
+        <v>0</v>
+      </c>
+      <c r="L194">
         <v>88</v>
       </c>
-      <c r="L194">
+      <c r="M194">
         <v>88</v>
       </c>
     </row>
@@ -8498,15 +9107,18 @@
         <v>demo-bud-3</v>
       </c>
       <c r="I195" t="str">
-        <v>Budgets: demo-bud-3</v>
-      </c>
-      <c r="J195" t="b">
-        <v>0</v>
-      </c>
-      <c r="K195">
+        <v>Spend note · Taxi</v>
+      </c>
+      <c r="J195" t="str">
+        <v>Spend note · Taxi | Budgets: demo-bud-3</v>
+      </c>
+      <c r="K195" t="b">
+        <v>0</v>
+      </c>
+      <c r="L195">
         <v>92</v>
       </c>
-      <c r="L195">
+      <c r="M195">
         <v>92</v>
       </c>
     </row>
@@ -8536,15 +9148,18 @@
         <v>demo-bud-5</v>
       </c>
       <c r="I196" t="str">
-        <v>Budgets: demo-bud-5</v>
-      </c>
-      <c r="J196" t="b">
-        <v>0</v>
-      </c>
-      <c r="K196">
+        <v>Spend note · Water bill share</v>
+      </c>
+      <c r="J196" t="str">
+        <v>Spend note · Water bill share | Budgets: demo-bud-5</v>
+      </c>
+      <c r="K196" t="b">
+        <v>0</v>
+      </c>
+      <c r="L196">
         <v>97</v>
       </c>
-      <c r="L196">
+      <c r="M196">
         <v>97</v>
       </c>
     </row>
@@ -8574,15 +9189,18 @@
         <v/>
       </c>
       <c r="I197" t="str">
-        <v/>
-      </c>
-      <c r="J197" t="b">
-        <v>0</v>
-      </c>
-      <c r="K197">
+        <v>Spend note · Office supplies</v>
+      </c>
+      <c r="J197" t="str">
+        <v>Spend note · Office supplies</v>
+      </c>
+      <c r="K197" t="b">
+        <v>0</v>
+      </c>
+      <c r="L197">
         <v>102</v>
       </c>
-      <c r="L197">
+      <c r="M197">
         <v>102</v>
       </c>
     </row>
@@ -8612,15 +9230,18 @@
         <v>demo-bud-1</v>
       </c>
       <c r="I198" t="str">
-        <v>Budgets: demo-bud-1</v>
-      </c>
-      <c r="J198" t="b">
-        <v>0</v>
-      </c>
-      <c r="K198">
+        <v>Spend note · Yoga · reviewed</v>
+      </c>
+      <c r="J198" t="str">
+        <v>Spend note · Yoga · reviewed | Budgets: demo-bud-1</v>
+      </c>
+      <c r="K198" t="b">
+        <v>0</v>
+      </c>
+      <c r="L198">
         <v>106</v>
       </c>
-      <c r="L198">
+      <c r="M198">
         <v>106</v>
       </c>
     </row>
@@ -8650,15 +9271,18 @@
         <v>demo-bud-2</v>
       </c>
       <c r="I199" t="str">
-        <v>Budgets: demo-bud-2</v>
-      </c>
-      <c r="J199" t="b">
-        <v>0</v>
-      </c>
-      <c r="K199">
+        <v>Spend note · Dentist</v>
+      </c>
+      <c r="J199" t="str">
+        <v>Spend note · Dentist | Budgets: demo-bud-2</v>
+      </c>
+      <c r="K199" t="b">
+        <v>0</v>
+      </c>
+      <c r="L199">
         <v>111</v>
       </c>
-      <c r="L199">
+      <c r="M199">
         <v>111</v>
       </c>
     </row>
@@ -8688,15 +9312,18 @@
         <v>demo-bud-1,demo-bud-6</v>
       </c>
       <c r="I200" t="str">
-        <v>Budgets: demo-bud-1,demo-bud-6</v>
-      </c>
-      <c r="J200" t="b">
-        <v>0</v>
-      </c>
-      <c r="K200">
+        <v>Spend note · Home goods</v>
+      </c>
+      <c r="J200" t="str">
+        <v>Spend note · Home goods | Budgets: demo-bud-1,demo-bud-6</v>
+      </c>
+      <c r="K200" t="b">
+        <v>0</v>
+      </c>
+      <c r="L200">
         <v>115</v>
       </c>
-      <c r="L200">
+      <c r="M200">
         <v>115</v>
       </c>
     </row>
@@ -8726,21 +9353,24 @@
         <v>demo-bud-4</v>
       </c>
       <c r="I201" t="str">
-        <v>Budgets: demo-bud-4</v>
-      </c>
-      <c r="J201" t="b">
-        <v>0</v>
-      </c>
-      <c r="K201">
-        <v>120</v>
+        <v>Spend note · Takeout</v>
+      </c>
+      <c r="J201" t="str">
+        <v>Spend note · Takeout | Budgets: demo-bud-4</v>
+      </c>
+      <c r="K201" t="b">
+        <v>0</v>
       </c>
       <c r="L201">
         <v>120</v>
       </c>
+      <c r="M201">
+        <v>120</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M201"/>
   </ignoredErrors>
 </worksheet>
 </file>
